--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/68.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/68.xlsx
@@ -426,13 +426,13 @@
         <v>-5.512076863539789</v>
       </c>
       <c r="E2">
-        <v>-5.225729755812972</v>
+        <v>-6.320900438301979</v>
       </c>
       <c r="F2">
-        <v>-3.506736157192683</v>
+        <v>-3.743717988887774</v>
       </c>
       <c r="G2">
-        <v>-11.11715405773153</v>
+        <v>-12.57360208336957</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.348066707259671</v>
       </c>
       <c r="E3">
-        <v>-4.389746283152978</v>
+        <v>-6.308791298805469</v>
       </c>
       <c r="F3">
-        <v>-3.437823444586389</v>
+        <v>-3.667935625410064</v>
       </c>
       <c r="G3">
-        <v>-11.10543803706804</v>
+        <v>-12.21974449176795</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.291326174679645</v>
       </c>
       <c r="E4">
-        <v>-4.942754472021667</v>
+        <v>-6.896220418606459</v>
       </c>
       <c r="F4">
-        <v>-3.318680189409139</v>
+        <v>-3.70417007234332</v>
       </c>
       <c r="G4">
-        <v>-10.43619139303114</v>
+        <v>-11.47596753600543</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.346928449412695</v>
       </c>
       <c r="E5">
-        <v>-6.5624990550852</v>
+        <v>-7.341432812196563</v>
       </c>
       <c r="F5">
-        <v>-3.775040217122429</v>
+        <v>-3.446410301083809</v>
       </c>
       <c r="G5">
-        <v>-10.19985816807365</v>
+        <v>-11.09975383037712</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.480124002786301</v>
       </c>
       <c r="E6">
-        <v>-6.769074453893099</v>
+        <v>-8.355869860076822</v>
       </c>
       <c r="F6">
-        <v>-3.446529585989812</v>
+        <v>-3.250133615194883</v>
       </c>
       <c r="G6">
-        <v>-10.18348089929087</v>
+        <v>-11.31306883220005</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.659483555792121</v>
       </c>
       <c r="E7">
-        <v>-7.464829200431573</v>
+        <v>-8.223661061422886</v>
       </c>
       <c r="F7">
-        <v>-3.067113292852957</v>
+        <v>-2.886138209628544</v>
       </c>
       <c r="G7">
-        <v>-9.916756866282871</v>
+        <v>-11.08458160017063</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.852718771600983</v>
       </c>
       <c r="E8">
-        <v>-8.230413016168324</v>
+        <v>-9.254310046250607</v>
       </c>
       <c r="F8">
-        <v>-2.928468612279001</v>
+        <v>-2.751991564051789</v>
       </c>
       <c r="G8">
-        <v>-9.922980691896701</v>
+        <v>-11.00450943521228</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.029449114448761</v>
       </c>
       <c r="E9">
-        <v>-8.483676981995304</v>
+        <v>-9.788855646590022</v>
       </c>
       <c r="F9">
-        <v>-3.092099338823599</v>
+        <v>-2.691568788956787</v>
       </c>
       <c r="G9">
-        <v>-9.926966588725984</v>
+        <v>-11.51287680822277</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.166154613761478</v>
       </c>
       <c r="E10">
-        <v>-8.678451177539213</v>
+        <v>-9.688875997448676</v>
       </c>
       <c r="F10">
-        <v>-2.223930539054383</v>
+        <v>-2.498890531065622</v>
       </c>
       <c r="G10">
-        <v>-10.43099052598894</v>
+        <v>-11.03976674520552</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.254784129553831</v>
       </c>
       <c r="E11">
-        <v>-9.754683781728142</v>
+        <v>-10.22730702848667</v>
       </c>
       <c r="F11">
-        <v>-2.111398484118875</v>
+        <v>-2.389837619221873</v>
       </c>
       <c r="G11">
-        <v>-11.46509901500001</v>
+        <v>-11.12571843904162</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.296608985845161</v>
       </c>
       <c r="E12">
-        <v>-10.64615011793011</v>
+        <v>-10.32817878700753</v>
       </c>
       <c r="F12">
-        <v>-2.059273465297716</v>
+        <v>-2.065599707152896</v>
       </c>
       <c r="G12">
-        <v>-10.83364224829388</v>
+        <v>-11.97864739177945</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.299568175341809</v>
       </c>
       <c r="E13">
-        <v>-11.23453927422073</v>
+        <v>-11.15599289255769</v>
       </c>
       <c r="F13">
-        <v>-1.815737590711676</v>
+        <v>-1.475477396337751</v>
       </c>
       <c r="G13">
-        <v>-10.09287126788102</v>
+        <v>-10.61533825434326</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.280503178391394</v>
       </c>
       <c r="E14">
-        <v>-11.36019989945957</v>
+        <v>-11.60266345477826</v>
       </c>
       <c r="F14">
-        <v>-1.701125505227739</v>
+        <v>-1.582246499251982</v>
       </c>
       <c r="G14">
-        <v>-10.33238592710175</v>
+        <v>-10.1821765443484</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.26170317718557</v>
       </c>
       <c r="E15">
-        <v>-12.27127905658877</v>
+        <v>-13.2700521128765</v>
       </c>
       <c r="F15">
-        <v>-1.088060730824658</v>
+        <v>-1.155626518034</v>
       </c>
       <c r="G15">
-        <v>-9.781726334827077</v>
+        <v>-10.32398376252308</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.260381287030455</v>
       </c>
       <c r="E16">
-        <v>-12.49056135346219</v>
+        <v>-13.29822374967821</v>
       </c>
       <c r="F16">
-        <v>-0.866582623440363</v>
+        <v>-0.891661446560118</v>
       </c>
       <c r="G16">
-        <v>-9.565388804926785</v>
+        <v>-10.31790229036744</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.289343130340391</v>
       </c>
       <c r="E17">
-        <v>-13.09596398659962</v>
+        <v>-14.03352113125166</v>
       </c>
       <c r="F17">
-        <v>-0.5064697758909451</v>
+        <v>-0.6390624042200479</v>
       </c>
       <c r="G17">
-        <v>-8.756715224957933</v>
+        <v>-9.746207491736238</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.355680355903251</v>
       </c>
       <c r="E18">
-        <v>-14.76610595689452</v>
+        <v>-15.25379996515058</v>
       </c>
       <c r="F18">
-        <v>-0.1916437742525762</v>
+        <v>-0.01946015427407374</v>
       </c>
       <c r="G18">
-        <v>-9.081403599813033</v>
+        <v>-9.510059657328945</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.45255909538733</v>
       </c>
       <c r="E19">
-        <v>-14.94940047082899</v>
+        <v>-16.89346983384786</v>
       </c>
       <c r="F19">
-        <v>-0.09484655813324555</v>
+        <v>-0.07116519082201328</v>
       </c>
       <c r="G19">
-        <v>-8.698290717280875</v>
+        <v>-9.55373899517409</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.56710205695488</v>
       </c>
       <c r="E20">
-        <v>-16.86386267078571</v>
+        <v>-16.55407429239499</v>
       </c>
       <c r="F20">
-        <v>-0.1084259849673378</v>
+        <v>0.3577642787149735</v>
       </c>
       <c r="G20">
-        <v>-9.040640852587988</v>
+        <v>-9.034072730238073</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.693576394985492</v>
       </c>
       <c r="E21">
-        <v>-17.36496549057848</v>
+        <v>-17.62996726103335</v>
       </c>
       <c r="F21">
-        <v>0.09887461431804404</v>
+        <v>0.20686721588621</v>
       </c>
       <c r="G21">
-        <v>-8.216910911506531</v>
+        <v>-8.500886197319673</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.834831892319738</v>
       </c>
       <c r="E22">
-        <v>-17.90499507294119</v>
+        <v>-17.83082319716956</v>
       </c>
       <c r="F22">
-        <v>0.5352958386459495</v>
+        <v>0.6670965477379761</v>
       </c>
       <c r="G22">
-        <v>-8.574423345383504</v>
+        <v>-8.795998158326924</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.992989091678868</v>
       </c>
       <c r="E23">
-        <v>-18.32905496444146</v>
+        <v>-18.23057424019666</v>
       </c>
       <c r="F23">
-        <v>0.9373563831057317</v>
+        <v>0.9186004883715452</v>
       </c>
       <c r="G23">
-        <v>-8.193882756735359</v>
+        <v>-8.765613971367493</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.170746716085892</v>
       </c>
       <c r="E24">
-        <v>-18.0171744310592</v>
+        <v>-19.63789716450839</v>
       </c>
       <c r="F24">
-        <v>0.5845638182948529</v>
+        <v>0.6525098261420796</v>
       </c>
       <c r="G24">
-        <v>-8.388211779890579</v>
+        <v>-8.617539890486972</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.370929348564809</v>
       </c>
       <c r="E25">
-        <v>-19.15236323835399</v>
+        <v>-19.49789939056126</v>
       </c>
       <c r="F25">
-        <v>0.6188325493812658</v>
+        <v>0.921675388170737</v>
       </c>
       <c r="G25">
-        <v>-7.572566191016022</v>
+        <v>-9.0867368886768</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.588762797471984</v>
       </c>
       <c r="E26">
-        <v>-19.21727438477994</v>
+        <v>-18.77909923979775</v>
       </c>
       <c r="F26">
-        <v>0.5993899380701585</v>
+        <v>1.131335177819292</v>
       </c>
       <c r="G26">
-        <v>-7.955689005184798</v>
+        <v>-8.037886540379363</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.810937776544457</v>
       </c>
       <c r="E27">
-        <v>-19.58680692075385</v>
+        <v>-19.65170901023178</v>
       </c>
       <c r="F27">
-        <v>0.743288124712669</v>
+        <v>1.087010894830296</v>
       </c>
       <c r="G27">
-        <v>-7.834337647897273</v>
+        <v>-7.515432796099279</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.023580254024713</v>
       </c>
       <c r="E28">
-        <v>-18.93065820788647</v>
+        <v>-19.52187766043188</v>
       </c>
       <c r="F28">
-        <v>0.1191605036452011</v>
+        <v>0.7350061074194796</v>
       </c>
       <c r="G28">
-        <v>-8.087759908928483</v>
+        <v>-8.654594826708035</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.214101853801507</v>
       </c>
       <c r="E29">
-        <v>-19.24410559327539</v>
+        <v>-20.20683652493607</v>
       </c>
       <c r="F29">
-        <v>0.08895408630211715</v>
+        <v>0.6994575486957416</v>
       </c>
       <c r="G29">
-        <v>-7.22530982721971</v>
+        <v>-8.618787966155278</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.366963978685256</v>
       </c>
       <c r="E30">
-        <v>-19.10941971933925</v>
+        <v>-19.79044786840478</v>
       </c>
       <c r="F30">
-        <v>0.1853420889244648</v>
+        <v>0.4817965583035463</v>
       </c>
       <c r="G30">
-        <v>-7.220615473645023</v>
+        <v>-8.46315259926306</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.4694582295839</v>
       </c>
       <c r="E31">
-        <v>-19.71212791044212</v>
+        <v>-20.43709131433007</v>
       </c>
       <c r="F31">
-        <v>0.1762739509660186</v>
+        <v>0.4030975132005793</v>
       </c>
       <c r="G31">
-        <v>-7.428766024426699</v>
+        <v>-8.0632386981191</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.515875289697011</v>
       </c>
       <c r="E32">
-        <v>-18.64605720192641</v>
+        <v>-19.38938809638946</v>
       </c>
       <c r="F32">
-        <v>-0.1276275413642304</v>
+        <v>0.4673092407959857</v>
       </c>
       <c r="G32">
-        <v>-7.116816628806715</v>
+        <v>-8.391214444694697</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.499608810326226</v>
       </c>
       <c r="E33">
-        <v>-18.56819009136451</v>
+        <v>-18.15817299776203</v>
       </c>
       <c r="F33">
-        <v>-0.2184704525922382</v>
+        <v>0.5375456845119531</v>
       </c>
       <c r="G33">
-        <v>-5.97016283364259</v>
+        <v>-8.005175039905824</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.415371050967703</v>
       </c>
       <c r="E34">
-        <v>-18.7710385560641</v>
+        <v>-19.16131150299315</v>
       </c>
       <c r="F34">
-        <v>-0.03084192238853894</v>
+        <v>0.2579368946362023</v>
       </c>
       <c r="G34">
-        <v>-6.825770017721688</v>
+        <v>-7.760135080180049</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.271528722221582</v>
       </c>
       <c r="E35">
-        <v>-18.64441789433563</v>
+        <v>-19.37837484760281</v>
       </c>
       <c r="F35">
-        <v>0.135852935179014</v>
+        <v>0.1583323413887842</v>
       </c>
       <c r="G35">
-        <v>-6.999404820710923</v>
+        <v>-7.830374924886765</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.084718776582864</v>
       </c>
       <c r="E36">
-        <v>-18.65492395403342</v>
+        <v>-18.91894757410263</v>
       </c>
       <c r="F36">
-        <v>-0.02380825477136834</v>
+        <v>0.1826134466996433</v>
       </c>
       <c r="G36">
-        <v>-5.904127381770747</v>
+        <v>-7.865940115615156</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.871377434303048</v>
       </c>
       <c r="E37">
-        <v>-17.59111748252154</v>
+        <v>-17.67015746785142</v>
       </c>
       <c r="F37">
-        <v>0.1208478880447037</v>
+        <v>0.4973425293518846</v>
       </c>
       <c r="G37">
-        <v>-6.10988109758199</v>
+        <v>-7.267605357029439</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.650360350120939</v>
       </c>
       <c r="E38">
-        <v>-16.9243087418401</v>
+        <v>-18.6935790081629</v>
       </c>
       <c r="F38">
-        <v>-0.3072739232745536</v>
+        <v>0.3432429981438982</v>
       </c>
       <c r="G38">
-        <v>-5.855088270697523</v>
+        <v>-7.347551721257298</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.441471102944888</v>
       </c>
       <c r="E39">
-        <v>-15.99360770683567</v>
+        <v>-17.63736678756188</v>
       </c>
       <c r="F39">
-        <v>-0.1271354911269675</v>
+        <v>0.396533529900796</v>
       </c>
       <c r="G39">
-        <v>-5.855876180535869</v>
+        <v>-7.495463585406396</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.252194536273446</v>
       </c>
       <c r="E40">
-        <v>-16.64686725328617</v>
+        <v>-17.0312894117973</v>
       </c>
       <c r="F40">
-        <v>-0.1253097693711974</v>
+        <v>-0.1450630184583544</v>
       </c>
       <c r="G40">
-        <v>-5.894818127714316</v>
+        <v>-6.765607473636513</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.07613938988528</v>
       </c>
       <c r="E41">
-        <v>-15.15444524542229</v>
+        <v>-16.98002255755647</v>
       </c>
       <c r="F41">
-        <v>-0.03865259862953548</v>
+        <v>0.007671363269818469</v>
       </c>
       <c r="G41">
-        <v>-5.703898966464547</v>
+        <v>-6.59237655720307</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.905358386555895</v>
       </c>
       <c r="E42">
-        <v>-15.81334727048634</v>
+        <v>-16.65782163191072</v>
       </c>
       <c r="F42">
-        <v>-0.1765028748642068</v>
+        <v>0.08292522834454236</v>
       </c>
       <c r="G42">
-        <v>-5.937467885896747</v>
+        <v>-6.924010456599561</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.729476439334962</v>
       </c>
       <c r="E43">
-        <v>-15.36613781985886</v>
+        <v>-17.47717201954054</v>
       </c>
       <c r="F43">
-        <v>-0.1200363824849757</v>
+        <v>0.1884948552595198</v>
       </c>
       <c r="G43">
-        <v>-6.039091702315755</v>
+        <v>-6.950431920548485</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.536115538718855</v>
       </c>
       <c r="E44">
-        <v>-14.74322810620777</v>
+        <v>-16.69735973847169</v>
       </c>
       <c r="F44">
-        <v>-0.6889168679901334</v>
+        <v>-0.07068639446319516</v>
       </c>
       <c r="G44">
-        <v>-6.143549345716378</v>
+        <v>-6.310572989263688</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.318036170731951</v>
       </c>
       <c r="E45">
-        <v>-14.4972912113252</v>
+        <v>-16.60965678236514</v>
       </c>
       <c r="F45">
-        <v>-0.2973045215818615</v>
+        <v>-0.2797439610099148</v>
       </c>
       <c r="G45">
-        <v>-5.943426867867435</v>
+        <v>-6.514350309387988</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.074573335052781</v>
       </c>
       <c r="E46">
-        <v>-14.82441005974328</v>
+        <v>-15.76857424797251</v>
       </c>
       <c r="F46">
-        <v>-0.7698491916110479</v>
+        <v>-0.08645271124067816</v>
       </c>
       <c r="G46">
-        <v>-6.415338513399464</v>
+        <v>-6.367335603080032</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.806833001747136</v>
       </c>
       <c r="E47">
-        <v>-14.44463864403802</v>
+        <v>-15.31630649187845</v>
       </c>
       <c r="F47">
-        <v>-0.6695504664800838</v>
+        <v>-0.499206650503199</v>
       </c>
       <c r="G47">
-        <v>-6.145548915222099</v>
+        <v>-6.802635925493261</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.514580129221152</v>
       </c>
       <c r="E48">
-        <v>-14.9518866030592</v>
+        <v>-15.16544490878692</v>
       </c>
       <c r="F48">
-        <v>-0.9550994790013098</v>
+        <v>-0.527276708314463</v>
       </c>
       <c r="G48">
-        <v>-6.110625970328327</v>
+        <v>-6.801480545100056</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.20622192785349</v>
       </c>
       <c r="E49">
-        <v>-13.15376542883353</v>
+        <v>-14.72133293438068</v>
       </c>
       <c r="F49">
-        <v>-1.079340507175388</v>
+        <v>-0.5005552326349566</v>
       </c>
       <c r="G49">
-        <v>-6.213375372230686</v>
+        <v>-6.239955742365495</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.889893404448067</v>
       </c>
       <c r="E50">
-        <v>-13.42125785999261</v>
+        <v>-14.63602101255018</v>
       </c>
       <c r="F50">
-        <v>-0.9435346416908258</v>
+        <v>-0.5426313264927547</v>
       </c>
       <c r="G50">
-        <v>-5.866946644819192</v>
+        <v>-6.321252809173378</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.57033854776708</v>
       </c>
       <c r="E51">
-        <v>-14.02757524487959</v>
+        <v>-15.18885711940658</v>
       </c>
       <c r="F51">
-        <v>-1.045779201850966</v>
+        <v>-0.9564538597048869</v>
       </c>
       <c r="G51">
-        <v>-6.647593146252574</v>
+        <v>-6.015500754802908</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.253826018920003</v>
       </c>
       <c r="E52">
-        <v>-13.26997965729237</v>
+        <v>-13.43638296317823</v>
       </c>
       <c r="F52">
-        <v>-0.759643705208558</v>
+        <v>-1.126466328720652</v>
       </c>
       <c r="G52">
-        <v>-6.102015241380682</v>
+        <v>-7.198746009812599</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.948297183302331</v>
       </c>
       <c r="E53">
-        <v>-13.0996682783379</v>
+        <v>-13.40249639217883</v>
       </c>
       <c r="F53">
-        <v>-1.589126918899634</v>
+        <v>-1.177075435194688</v>
       </c>
       <c r="G53">
-        <v>-6.569993958812057</v>
+        <v>-5.89166648836093</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.658946002550379</v>
       </c>
       <c r="E54">
-        <v>-12.80513180040501</v>
+        <v>-13.86031152893228</v>
       </c>
       <c r="F54">
-        <v>-0.9357107115713845</v>
+        <v>-0.8839982197168198</v>
       </c>
       <c r="G54">
-        <v>-5.956294958378582</v>
+        <v>-6.467049234722881</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.389214159784049</v>
       </c>
       <c r="E55">
-        <v>-12.39115229204581</v>
+        <v>-13.5811899765215</v>
       </c>
       <c r="F55">
-        <v>-1.093998468367925</v>
+        <v>-0.8211972018083808</v>
       </c>
       <c r="G55">
-        <v>-6.344370348674108</v>
+        <v>-6.24406743992527</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.146719551705158</v>
       </c>
       <c r="E56">
-        <v>-12.84865949256674</v>
+        <v>-13.34849433963736</v>
       </c>
       <c r="F56">
-        <v>-1.299422815485966</v>
+        <v>-1.209860560262686</v>
       </c>
       <c r="G56">
-        <v>-6.086472230073804</v>
+        <v>-5.555920891404664</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.938307009709719</v>
       </c>
       <c r="E57">
-        <v>-12.54157008468459</v>
+        <v>-12.81024444755967</v>
       </c>
       <c r="F57">
-        <v>-1.333362684713468</v>
+        <v>-0.9240100220068415</v>
       </c>
       <c r="G57">
-        <v>-6.63647964487724</v>
+        <v>-5.842511508193832</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.766616748281084</v>
       </c>
       <c r="E58">
-        <v>-11.99799017869987</v>
+        <v>-12.97112754363017</v>
       </c>
       <c r="F58">
-        <v>-1.303460278207211</v>
+        <v>-0.9262209346049134</v>
       </c>
       <c r="G58">
-        <v>-7.390873520184202</v>
+        <v>-5.939490629221241</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.63337881345658</v>
       </c>
       <c r="E59">
-        <v>-12.08215186813242</v>
+        <v>-12.94766551979643</v>
       </c>
       <c r="F59">
-        <v>-0.9247671498130002</v>
+        <v>-1.013079398625456</v>
       </c>
       <c r="G59">
-        <v>-6.413233006436488</v>
+        <v>-6.819609092473105</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.534290980521167</v>
       </c>
       <c r="E60">
-        <v>-12.02131634831338</v>
+        <v>-12.34251648120343</v>
       </c>
       <c r="F60">
-        <v>-1.148901003090671</v>
+        <v>-0.8891382394511907</v>
       </c>
       <c r="G60">
-        <v>-6.488249968356373</v>
+        <v>-6.215067061001254</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.458309409216803</v>
       </c>
       <c r="E61">
-        <v>-12.47318107022075</v>
+        <v>-12.70442306694843</v>
       </c>
       <c r="F61">
-        <v>-1.164727790688558</v>
+        <v>-0.6938150044428869</v>
       </c>
       <c r="G61">
-        <v>-6.665089379427622</v>
+        <v>-6.508510507056712</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.392907177437404</v>
       </c>
       <c r="E62">
-        <v>-12.60731899880195</v>
+        <v>-12.4458155017924</v>
       </c>
       <c r="F62">
-        <v>-1.034100049838896</v>
+        <v>-1.091789212504659</v>
       </c>
       <c r="G62">
-        <v>-6.837082151829378</v>
+        <v>-6.887759982944542</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.329526734091924</v>
       </c>
       <c r="E63">
-        <v>-11.13098665908733</v>
+        <v>-13.13797011149477</v>
       </c>
       <c r="F63">
-        <v>-1.310715948288332</v>
+        <v>-1.016952016233543</v>
       </c>
       <c r="G63">
-        <v>-6.988172139696176</v>
+        <v>-6.956546498159518</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.262538203437058</v>
       </c>
       <c r="E64">
-        <v>-11.30090406080314</v>
+        <v>-12.46034737488301</v>
       </c>
       <c r="F64">
-        <v>-1.04522999426291</v>
+        <v>-0.9028129285366049</v>
       </c>
       <c r="G64">
-        <v>-5.996537949953963</v>
+        <v>-6.420539380441659</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.187617629540752</v>
       </c>
       <c r="E65">
-        <v>-11.22832620788221</v>
+        <v>-12.74204110053015</v>
       </c>
       <c r="F65">
-        <v>-1.06373240857184</v>
+        <v>-0.6582714159235656</v>
       </c>
       <c r="G65">
-        <v>-6.024263768845359</v>
+        <v>-7.444064055363672</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.104831424100285</v>
       </c>
       <c r="E66">
-        <v>-10.29252611114514</v>
+        <v>-11.82014794747064</v>
       </c>
       <c r="F66">
-        <v>-1.389599719322123</v>
+        <v>-0.7732015944901774</v>
       </c>
       <c r="G66">
-        <v>-6.87659020229504</v>
+        <v>-6.969897928319399</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.016885502334508</v>
       </c>
       <c r="E67">
-        <v>-11.49572354108713</v>
+        <v>-11.35414985818533</v>
       </c>
       <c r="F67">
-        <v>-1.401404783179419</v>
+        <v>-1.164239882288309</v>
       </c>
       <c r="G67">
-        <v>-6.97162272254536</v>
+        <v>-7.642087647340717</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.926312805558309</v>
       </c>
       <c r="E68">
-        <v>-11.25191502898816</v>
+        <v>-11.98298734431246</v>
       </c>
       <c r="F68">
-        <v>-1.164568744147221</v>
+        <v>-1.071313627042261</v>
       </c>
       <c r="G68">
-        <v>-6.922196277644041</v>
+        <v>-7.630778823778567</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.833939668634797</v>
       </c>
       <c r="E69">
-        <v>-10.12691981668464</v>
+        <v>-11.17313316667672</v>
       </c>
       <c r="F69">
-        <v>-1.330894149853125</v>
+        <v>-1.040506643332147</v>
       </c>
       <c r="G69">
-        <v>-6.969517215582383</v>
+        <v>-6.78374264210064</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.738743143277051</v>
       </c>
       <c r="E70">
-        <v>-11.16812467442424</v>
+        <v>-11.89013098478518</v>
       </c>
       <c r="F70">
-        <v>-1.157312245698697</v>
+        <v>-0.9153693216282398</v>
       </c>
       <c r="G70">
-        <v>-6.859875257867261</v>
+        <v>-7.120686656542123</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.636508518811857</v>
       </c>
       <c r="E71">
-        <v>-11.50343100384818</v>
+        <v>-11.8867799140195</v>
       </c>
       <c r="F71">
-        <v>-1.050484328698867</v>
+        <v>-1.323473634658847</v>
       </c>
       <c r="G71">
-        <v>-7.377244004199022</v>
+        <v>-7.355616210190964</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.521992959095076</v>
       </c>
       <c r="E72">
-        <v>-10.92812008049172</v>
+        <v>-11.81350467610139</v>
       </c>
       <c r="F72">
-        <v>-1.566660766568309</v>
+        <v>-1.195590275014659</v>
       </c>
       <c r="G72">
-        <v>-6.445537309808696</v>
+        <v>-7.096231656643527</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.393101933122818</v>
       </c>
       <c r="E73">
-        <v>-11.5687995261489</v>
+        <v>-12.31416823391541</v>
       </c>
       <c r="F73">
-        <v>-1.549435694794496</v>
+        <v>-0.9022570940093265</v>
       </c>
       <c r="G73">
-        <v>-6.546743997489756</v>
+        <v>-7.332713856150285</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.249558988973288</v>
       </c>
       <c r="E74">
-        <v>-11.43520954292263</v>
+        <v>-13.33129972383024</v>
       </c>
       <c r="F74">
-        <v>-1.315773959649826</v>
+        <v>-1.440458164384402</v>
       </c>
       <c r="G74">
-        <v>-5.939778646683158</v>
+        <v>-6.599821974120891</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.092384687183842</v>
       </c>
       <c r="E75">
-        <v>-11.19856054822979</v>
+        <v>-11.2130924213204</v>
       </c>
       <c r="F75">
-        <v>-1.547976111430764</v>
+        <v>-1.491700143554176</v>
       </c>
       <c r="G75">
-        <v>-5.800007414015129</v>
+        <v>-6.56076415784857</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.9232769810032827</v>
       </c>
       <c r="E76">
-        <v>-10.62271073646641</v>
+        <v>-12.18670527602151</v>
       </c>
       <c r="F76">
-        <v>-1.593571110015654</v>
+        <v>-1.368177309918325</v>
       </c>
       <c r="G76">
-        <v>-6.378995344469345</v>
+        <v>-6.057547993697192</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.7456356794928302</v>
       </c>
       <c r="E77">
-        <v>-12.0575214980047</v>
+        <v>-13.48987782663084</v>
       </c>
       <c r="F77">
-        <v>-1.354119915092818</v>
+        <v>-1.348541689002366</v>
       </c>
       <c r="G77">
-        <v>-5.432371331879064</v>
+        <v>-6.58964866767871</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.5613679104891336</v>
       </c>
       <c r="E78">
-        <v>-13.59474822770047</v>
+        <v>-14.19967084259309</v>
       </c>
       <c r="F78">
-        <v>-2.015405612747663</v>
+        <v>-1.521085648801086</v>
       </c>
       <c r="G78">
-        <v>-6.138027355756874</v>
+        <v>-5.77493003155515</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.372610723085404</v>
       </c>
       <c r="E79">
-        <v>-13.36089330147036</v>
+        <v>-14.90748038693998</v>
       </c>
       <c r="F79">
-        <v>-1.916814152833868</v>
+        <v>-1.284618233263134</v>
       </c>
       <c r="G79">
-        <v>-5.596213541163134</v>
+        <v>-6.393439254657186</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.1843087123350656</v>
       </c>
       <c r="E80">
-        <v>-13.32501420190759</v>
+        <v>-14.79878342533387</v>
       </c>
       <c r="F80">
-        <v>-1.964123043575151</v>
+        <v>-1.674516687515013</v>
       </c>
       <c r="G80">
-        <v>-4.880996661767908</v>
+        <v>-6.238562002693461</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.0002154113344351275</v>
       </c>
       <c r="E81">
-        <v>-14.00552610493625</v>
+        <v>-15.23997453400516</v>
       </c>
       <c r="F81">
-        <v>-1.961623030753502</v>
+        <v>-1.626265114669345</v>
       </c>
       <c r="G81">
-        <v>-5.359340697282741</v>
+        <v>-5.889468286122854</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.1748500747919942</v>
       </c>
       <c r="E82">
-        <v>-14.1724003721189</v>
+        <v>-15.60222075530074</v>
       </c>
       <c r="F82">
-        <v>-1.858429989917157</v>
+        <v>-1.586138997677737</v>
       </c>
       <c r="G82">
-        <v>-5.14498949470601</v>
+        <v>-5.736342312749405</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.3359103511260009</v>
       </c>
       <c r="E83">
-        <v>-14.90388477857789</v>
+        <v>-16.03758824639817</v>
       </c>
       <c r="F83">
-        <v>-2.030992173798738</v>
+        <v>-1.755711603602615</v>
       </c>
       <c r="G83">
-        <v>-5.474332496589326</v>
+        <v>-5.113953130275343</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.476424470011416</v>
       </c>
       <c r="E84">
-        <v>-17.06748550454061</v>
+        <v>-17.9044697699563</v>
       </c>
       <c r="F84">
-        <v>-2.150214952246657</v>
+        <v>-1.646166641521603</v>
       </c>
       <c r="G84">
-        <v>-5.099856827369126</v>
+        <v>-5.227557811000973</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.5894761653949052</v>
       </c>
       <c r="E85">
-        <v>-18.14889868299431</v>
+        <v>-18.06659819637892</v>
       </c>
       <c r="F85">
-        <v>-1.9547575217191</v>
+        <v>-2.024906986857773</v>
       </c>
       <c r="G85">
-        <v>-5.331555288571638</v>
+        <v>-5.215232649958266</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.6679001371018678</v>
       </c>
       <c r="E86">
-        <v>-18.09625064418114</v>
+        <v>-19.79387139475458</v>
       </c>
       <c r="F86">
-        <v>-2.678378694802011</v>
+        <v>-2.271790294118527</v>
       </c>
       <c r="G86">
-        <v>-4.30383284190583</v>
+        <v>-4.648454011452882</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.7043929657357119</v>
       </c>
       <c r="E87">
-        <v>-19.82147697230534</v>
+        <v>-19.81674471696732</v>
       </c>
       <c r="F87">
-        <v>-2.742991352220372</v>
+        <v>-2.557595272167218</v>
       </c>
       <c r="G87">
-        <v>-4.669426317444165</v>
+        <v>-5.105504618059123</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.6915233635271678</v>
       </c>
       <c r="E88">
-        <v>-20.78972358530736</v>
+        <v>-22.21309994997629</v>
       </c>
       <c r="F88">
-        <v>-2.541548138840186</v>
+        <v>-2.318168099899063</v>
       </c>
       <c r="G88">
-        <v>-4.813683339317907</v>
+        <v>-4.502088172070624</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.6244199429017385</v>
       </c>
       <c r="E89">
-        <v>-21.35894371112351</v>
+        <v>-23.28829553361746</v>
       </c>
       <c r="F89">
-        <v>-2.486932219238809</v>
+        <v>-2.704647881879589</v>
       </c>
       <c r="G89">
-        <v>-4.545436455361841</v>
+        <v>-5.347588260618329</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.5009240370080676</v>
       </c>
       <c r="E90">
-        <v>-23.8330120865781</v>
+        <v>-24.76066998704938</v>
       </c>
       <c r="F90">
-        <v>-2.819870474139389</v>
+        <v>-2.120320001047026</v>
       </c>
       <c r="G90">
-        <v>-4.629759360792618</v>
+        <v>-5.441548164113923</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.3199256530311551</v>
       </c>
       <c r="E91">
-        <v>-24.85141154921507</v>
+        <v>-27.6082967118707</v>
       </c>
       <c r="F91">
-        <v>-2.631258671828566</v>
+        <v>-2.69906468558472</v>
       </c>
       <c r="G91">
-        <v>-4.687826329551434</v>
+        <v>-4.823869887942244</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.0816909151221578</v>
       </c>
       <c r="E92">
-        <v>-27.99289548086814</v>
+        <v>-29.16871375695975</v>
       </c>
       <c r="F92">
-        <v>-2.933402368530075</v>
+        <v>-2.85479858567843</v>
       </c>
       <c r="G92">
-        <v>-4.67758019110739</v>
+        <v>-5.803188848278369</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.2110540003274781</v>
       </c>
       <c r="E93">
-        <v>-29.84118535438778</v>
+        <v>-30.24500975978479</v>
       </c>
       <c r="F93">
-        <v>-2.887007995401483</v>
+        <v>-2.572082589674778</v>
       </c>
       <c r="G93">
-        <v>-4.600120046579523</v>
+        <v>-5.052194903240239</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.5534093900280947</v>
       </c>
       <c r="E94">
-        <v>-31.80353843121263</v>
+        <v>-32.14811907540428</v>
       </c>
       <c r="F94">
-        <v>-2.650275502294635</v>
+        <v>-2.748980448542613</v>
       </c>
       <c r="G94">
-        <v>-4.724619732674895</v>
+        <v>-5.846623205753606</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.9411526401836624</v>
       </c>
       <c r="E95">
-        <v>-34.31762493147301</v>
+        <v>-34.5926255725368</v>
       </c>
       <c r="F95">
-        <v>-2.730873165484818</v>
+        <v>-2.878753314232586</v>
       </c>
       <c r="G95">
-        <v>-5.044252904491527</v>
+        <v>-5.653581984813164</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.370067760220969</v>
       </c>
       <c r="E96">
-        <v>-35.61193072997531</v>
+        <v>-36.95520518215955</v>
       </c>
       <c r="F96">
-        <v>-2.99968501463248</v>
+        <v>-3.01810459220113</v>
       </c>
       <c r="G96">
-        <v>-4.579256988591036</v>
+        <v>-5.824230675725977</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.826046442954943</v>
       </c>
       <c r="E97">
-        <v>-37.74098146349651</v>
+        <v>-38.28270243090108</v>
       </c>
       <c r="F97">
-        <v>-2.658825910626331</v>
+        <v>-3.241714088912829</v>
       </c>
       <c r="G97">
-        <v>-5.913221450367125</v>
+        <v>-6.449814534645435</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.304355123991097</v>
       </c>
       <c r="E98">
-        <v>-40.02682381682228</v>
+        <v>-41.67981645605013</v>
       </c>
       <c r="F98">
-        <v>-2.95803138815011</v>
+        <v>-3.245908941440605</v>
       </c>
       <c r="G98">
-        <v>-5.825468819757663</v>
+        <v>-6.242057938782932</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.778890681463916</v>
       </c>
       <c r="E99">
-        <v>-43.42593037053471</v>
+        <v>-42.921324776097</v>
       </c>
       <c r="F99">
-        <v>-2.881887028117377</v>
+        <v>-3.476934811509568</v>
       </c>
       <c r="G99">
-        <v>-6.34572436179967</v>
+        <v>-6.910000227877365</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.249990842036922</v>
       </c>
       <c r="E100">
-        <v>-45.60884730237715</v>
+        <v>-45.29380815837453</v>
       </c>
       <c r="F100">
-        <v>-3.071716530510314</v>
+        <v>-3.384498121398574</v>
       </c>
       <c r="G100">
-        <v>-6.807823550353299</v>
+        <v>-7.221069018383904</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.668182217772695</v>
       </c>
       <c r="E101">
-        <v>-46.91862689656366</v>
+        <v>-48.73046708279556</v>
       </c>
       <c r="F101">
-        <v>-2.998154191672107</v>
+        <v>-3.331764252536357</v>
       </c>
       <c r="G101">
-        <v>-7.080857483159151</v>
+        <v>-7.879847717425634</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.064997237847847</v>
       </c>
       <c r="E102">
-        <v>-49.30093140684532</v>
+        <v>-50.45319369326753</v>
       </c>
       <c r="F102">
-        <v>-2.909512252633337</v>
+        <v>-3.554027652218507</v>
       </c>
       <c r="G102">
-        <v>-8.308311763300269</v>
+        <v>-7.629391705197612</v>
       </c>
     </row>
   </sheetData>
